--- a/01_analyses_states/Goa/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Goa/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4">
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -440,7 +440,7 @@
         <v>33.3</v>
       </c>
       <c r="E4">
-        <v>28.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="E6">
-        <v>28.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C8">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -778,19 +778,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Trend Different</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>IUCN</t>
         </is>
       </c>
-      <c r="B3">
-        <v>29</v>
-      </c>
-      <c r="C3">
-        <v>28.2</v>
-      </c>
-      <c r="D3">
+      <c r="B4">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>27.2</v>
+      </c>
+      <c r="D4">
         <v>19</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>20.4</v>
       </c>
     </row>

--- a/01_analyses_states/Goa/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Goa/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>12.5</v>
-      </c>
-      <c r="E3">
-        <v>6.7</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>12.5</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="E6">
-        <v>13.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C8">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -778,19 +778,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Trend Different</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>IUCN</t>
         </is>
       </c>
-      <c r="B3">
-        <v>29</v>
-      </c>
-      <c r="C3">
-        <v>28.2</v>
-      </c>
-      <c r="D3">
+      <c r="B4">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>27.2</v>
+      </c>
+      <c r="D4">
         <v>19</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>20.4</v>
       </c>
     </row>

--- a/01_analyses_states/Goa/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Goa/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C8">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -763,48 +763,35 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>79.59999999999999</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trend Different</t>
+          <t>IUCN</t>
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IUCN</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>28</v>
-      </c>
-      <c r="C4">
         <v>27.2</v>
       </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>20.4</v>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>
